--- a/ig/DM-SIDOBA/CodeSystem-tre-r413-categorie-permis-conduire.xlsx
+++ b/ig/DM-SIDOBA/CodeSystem-tre-r413-categorie-permis-conduire.xlsx
@@ -14,7 +14,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="84" uniqueCount="69">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="84" uniqueCount="73">
   <si>
     <t>Property</t>
   </si>
@@ -208,19 +208,31 @@
     <t>AM</t>
   </si>
   <si>
+    <t>Permis cyclomoteur</t>
+  </si>
+  <si>
     <t>B</t>
   </si>
   <si>
+    <t>Permis auto</t>
+  </si>
+  <si>
     <t>A</t>
   </si>
   <si>
+    <t>Permis moto</t>
+  </si>
+  <si>
     <t>CD</t>
   </si>
   <si>
-    <t>C et D</t>
+    <t>Permis professionnels</t>
   </si>
   <si>
     <t>E</t>
+  </si>
+  <si>
+    <t>Permis remorque</t>
   </si>
 </sst>
 </file>
@@ -663,7 +675,7 @@
         <v>63</v>
       </c>
       <c r="C2" t="s" s="2">
-        <v>63</v>
+        <v>64</v>
       </c>
       <c r="D2" s="2"/>
     </row>
@@ -672,10 +684,10 @@
         <v>62</v>
       </c>
       <c r="B3" t="s" s="2">
-        <v>64</v>
+        <v>65</v>
       </c>
       <c r="C3" t="s" s="2">
-        <v>64</v>
+        <v>66</v>
       </c>
       <c r="D3" s="2"/>
     </row>
@@ -684,10 +696,10 @@
         <v>62</v>
       </c>
       <c r="B4" t="s" s="2">
-        <v>65</v>
+        <v>67</v>
       </c>
       <c r="C4" t="s" s="2">
-        <v>65</v>
+        <v>68</v>
       </c>
       <c r="D4" s="2"/>
     </row>
@@ -696,10 +708,10 @@
         <v>62</v>
       </c>
       <c r="B5" t="s" s="2">
-        <v>66</v>
+        <v>69</v>
       </c>
       <c r="C5" t="s" s="2">
-        <v>67</v>
+        <v>70</v>
       </c>
       <c r="D5" s="2"/>
     </row>
@@ -708,10 +720,10 @@
         <v>62</v>
       </c>
       <c r="B6" t="s" s="2">
-        <v>68</v>
+        <v>71</v>
       </c>
       <c r="C6" t="s" s="2">
-        <v>68</v>
+        <v>72</v>
       </c>
       <c r="D6" s="2"/>
     </row>

--- a/ig/DM-SIDOBA/CodeSystem-tre-r413-categorie-permis-conduire.xlsx
+++ b/ig/DM-SIDOBA/CodeSystem-tre-r413-categorie-permis-conduire.xlsx
@@ -43,7 +43,7 @@
     <t>Name</t>
   </si>
   <si>
-    <t>TreR413TypeCategorieConduire</t>
+    <t>TreR413CategorieConduire</t>
   </si>
   <si>
     <t>Title</t>

--- a/ig/DM-SIDOBA/CodeSystem-tre-r413-categorie-permis-conduire.xlsx
+++ b/ig/DM-SIDOBA/CodeSystem-tre-r413-categorie-permis-conduire.xlsx
@@ -14,7 +14,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="84" uniqueCount="73">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="89" uniqueCount="78">
   <si>
     <t>Property</t>
   </si>
@@ -37,13 +37,13 @@
     <t>Version</t>
   </si>
   <si>
-    <t>20260505120000</t>
+    <t>20260601120000</t>
   </si>
   <si>
     <t>Name</t>
   </si>
   <si>
-    <t>TreR413CategorieConduire</t>
+    <t>TreR413CategoriePermisConduire</t>
   </si>
   <si>
     <t>Title</t>
@@ -67,7 +67,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2026-05-05T12:00:00.000+00:00</t>
+    <t>2026-06-01T12:00:00.000+00:00</t>
   </si>
   <si>
     <t>Publisher</t>
@@ -208,31 +208,46 @@
     <t>AM</t>
   </si>
   <si>
-    <t>Permis cyclomoteur</t>
+    <t>Catégorie AM, permis cyclomoteur</t>
+  </si>
+  <si>
+    <t>Cette catégorie (AM) permet de conduire dès 14 ans des cyclomoteurs (motocyclettes de moins de 50 cm3) et des voiturettes (quadricycles légers). Elle est délivrée à l’issue d’une formation d’une durée minimale de 8 heures. C’est la seule catégorie exclue du régime de permis à points.</t>
   </si>
   <si>
     <t>B</t>
   </si>
   <si>
-    <t>Permis auto</t>
+    <t>Catégorie B, permis auto</t>
+  </si>
+  <si>
+    <t>Être détenteur de la catégorie B permet de conduire des voitures dont le poids en charge est inférieur (PTAC) à 3,5 tonnes, et qui ne peuvent transporter plus de 8 passagers. Son obtention est soumise à des conditions d’âge, de formation et de réussite à un examen composé du code et d’une épreuve de conduite.</t>
   </si>
   <si>
     <t>A</t>
   </si>
   <si>
-    <t>Permis moto</t>
+    <t>Catégorie A, permis moto</t>
+  </si>
+  <si>
+    <t>Il existe trois catégories du permis moto : A1, A2 et A. Ces catégories requièrent différents examens et définissent la taille de la cylindrée autorisée à être conduite.</t>
   </si>
   <si>
     <t>CD</t>
   </si>
   <si>
-    <t>Permis professionnels</t>
+    <t>Catégorie C et D, permis professionnels</t>
+  </si>
+  <si>
+    <t>Le permis C autorise la conduite des véhicules affectés au transport de marchandises ou de matériel dont le poids total autorisé en charge (PTAC) est supérieur à 7,5 tonnes. Il existe différents permis dans cette catégorie : les permis C, C1 et C1E. Le permis D autorise la conduite des véhicules affectés au transport de personnes comportant plus de 8 places assises outre le siège du conducteur.</t>
   </si>
   <si>
     <t>E</t>
   </si>
   <si>
-    <t>Permis remorque</t>
+    <t>Catégorie E, permis remorque</t>
+  </si>
+  <si>
+    <t>Le permis E autorise la conduite des véhicules de catégorie B, C ou D attelés d’une remorque. On distingue donc trois permis E : le permis BE, le permis CE et le permis DE.</t>
   </si>
 </sst>
 </file>
@@ -677,55 +692,65 @@
       <c r="C2" t="s" s="2">
         <v>64</v>
       </c>
-      <c r="D2" s="2"/>
+      <c r="D2" t="s" s="2">
+        <v>65</v>
+      </c>
     </row>
     <row r="3">
       <c r="A3" t="s" s="2">
         <v>62</v>
       </c>
       <c r="B3" t="s" s="2">
-        <v>65</v>
+        <v>66</v>
       </c>
       <c r="C3" t="s" s="2">
-        <v>66</v>
-      </c>
-      <c r="D3" s="2"/>
+        <v>67</v>
+      </c>
+      <c r="D3" t="s" s="2">
+        <v>68</v>
+      </c>
     </row>
     <row r="4">
       <c r="A4" t="s" s="2">
         <v>62</v>
       </c>
       <c r="B4" t="s" s="2">
-        <v>67</v>
+        <v>69</v>
       </c>
       <c r="C4" t="s" s="2">
-        <v>68</v>
-      </c>
-      <c r="D4" s="2"/>
+        <v>70</v>
+      </c>
+      <c r="D4" t="s" s="2">
+        <v>71</v>
+      </c>
     </row>
     <row r="5">
       <c r="A5" t="s" s="2">
         <v>62</v>
       </c>
       <c r="B5" t="s" s="2">
-        <v>69</v>
+        <v>72</v>
       </c>
       <c r="C5" t="s" s="2">
-        <v>70</v>
-      </c>
-      <c r="D5" s="2"/>
+        <v>73</v>
+      </c>
+      <c r="D5" t="s" s="2">
+        <v>74</v>
+      </c>
     </row>
     <row r="6">
       <c r="A6" t="s" s="2">
         <v>62</v>
       </c>
       <c r="B6" t="s" s="2">
-        <v>71</v>
+        <v>75</v>
       </c>
       <c r="C6" t="s" s="2">
-        <v>72</v>
-      </c>
-      <c r="D6" s="2"/>
+        <v>76</v>
+      </c>
+      <c r="D6" t="s" s="2">
+        <v>77</v>
+      </c>
     </row>
   </sheetData>
   <pageMargins bottom="0.75" footer="0.3" header="0.3" left="0.7" right="0.7" top="0.75"/>
